--- a/Assets/Resources/Data/Excel/EnemyData.xlsx
+++ b/Assets/Resources/Data/Excel/EnemyData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\grunge\Assets\Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C7D83C2-28F9-4634-B266-08CACB93CDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2FBA52-1FD3-4868-A290-23765E161E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{66163B37-ABEE-48FD-BCF8-6B7CD202EEE3}"/>
+    <workbookView minimized="1" xWindow="21330" yWindow="150" windowWidth="18135" windowHeight="15525" xr2:uid="{66163B37-ABEE-48FD-BCF8-6B7CD202EEE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -35,63 +35,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>illustPath</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>acc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pro</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>crt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dmg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bleed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>blocksight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mark</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stun</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>down</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>move</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>death</t>
+    <t>nameIcon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spinePath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appearPercent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rowIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxHp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>minDmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxDmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Acc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spd</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -99,7 +91,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>resBlocksight</t>
+    <t>resBlock</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -115,15 +107,28 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>resDeath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>resMove</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>resDeath</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprites/Main/Battle/character_6</t>
+    <t>isBoss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DefaultSpinePath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>null</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spirtes/UI/Battle/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -487,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D8B22C-40E5-4862-8DBE-6C2511C3500A}">
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.45">
@@ -498,7 +503,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -510,76 +515,215 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2000</v>
+      </c>
       <c r="C2" t="s">
         <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2001</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2002</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2003</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>2004</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2005</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2006</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2007</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2008</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>2009</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>2010</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
